--- a/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Supplier & Distributor Research.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Supplier & Distributor Research.xlsx
@@ -205,7 +205,7 @@
     <t xml:space="preserve">Vía Agente Oficial</t>
   </si>
   <si>
-    <t xml:space="preserve">Registro FOLIO clase 34 en Cuba</t>
+    <t xml:space="preserve">Registro ARNALDO clase 34 en Cuba</t>
   </si>
   <si>
     <t xml:space="preserve">Búsqueda de anterioridades; plazos y tasas</t>
@@ -370,7 +370,7 @@
     <t xml:space="preserve">Online</t>
   </si>
   <si>
-    <t xml:space="preserve">Registro FOLIO</t>
+    <t xml:space="preserve">Registro ARNALDO</t>
   </si>
   <si>
     <t xml:space="preserve">Compañía de Distribución Integral Logista</t>

--- a/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Supplier & Distributor Research.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Supplier & Distributor Research.xlsx
@@ -205,7 +205,7 @@
     <t xml:space="preserve">Vía Agente Oficial</t>
   </si>
   <si>
-    <t xml:space="preserve">Registro ARNALDO clase 34 en Cuba</t>
+    <t xml:space="preserve">Registro ARNALDO VALLÉS clase 34 en Cuba</t>
   </si>
   <si>
     <t xml:space="preserve">Búsqueda de anterioridades; plazos y tasas</t>
@@ -370,7 +370,7 @@
     <t xml:space="preserve">Online</t>
   </si>
   <si>
-    <t xml:space="preserve">Registro ARNALDO</t>
+    <t xml:space="preserve">Registro ARNALDO VALLÉS</t>
   </si>
   <si>
     <t xml:space="preserve">Compañía de Distribución Integral Logista</t>
